--- a/material_order_forms/001_fabric_order_form--material_order_forms.xlsx
+++ b/material_order_forms/001_fabric_order_form--material_order_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1148,8 +1148,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
-    <col width="36" customWidth="1" min="2" max="2"/>
-    <col width="36" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1177,12 +1177,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'cotton'}</t>
+          <t>cotton</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'cotton'}</t>
+          <t>cotton</t>
         </is>
       </c>
     </row>
@@ -1194,12 +1194,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'polyester'}</t>
+          <t>polyester</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'polyester'}</t>
+          <t>polyester</t>
         </is>
       </c>
     </row>
@@ -1211,12 +1211,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'wool'}</t>
+          <t>wool</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'wool'}</t>
+          <t>wool</t>
         </is>
       </c>
     </row>
@@ -1228,12 +1228,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'red'}</t>
+          <t>red</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'red'}</t>
+          <t>red</t>
         </is>
       </c>
     </row>
@@ -1245,12 +1245,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'blue'}</t>
+          <t>blue</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'blue'}</t>
+          <t>blue</t>
         </is>
       </c>
     </row>
@@ -1262,12 +1262,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'green'}</t>
+          <t>green</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'green'}</t>
+          <t>green</t>
         </is>
       </c>
     </row>
@@ -1279,12 +1279,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'home'}</t>
+          <t>home</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'home'}</t>
+          <t>home</t>
         </is>
       </c>
     </row>
@@ -1296,12 +1296,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'work'}</t>
+          <t>work</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'work'}</t>
+          <t>work</t>
         </is>
       </c>
     </row>
@@ -1313,12 +1313,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'other'}</t>
+          <t>other</t>
         </is>
       </c>
     </row>
@@ -1330,12 +1330,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'pounds'}</t>
+          <t>pounds</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'pounds'}</t>
+          <t>pounds</t>
         </is>
       </c>
     </row>
@@ -1347,12 +1347,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'kilograms'}</t>
+          <t>kilograms</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'kilograms'}</t>
+          <t>kilograms</t>
         </is>
       </c>
     </row>
@@ -1364,12 +1364,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'ounces'}</t>
+          <t>ounces</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'ounces'}</t>
+          <t>ounces</t>
         </is>
       </c>
     </row>
@@ -1381,12 +1381,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'bank_transfer'}</t>
+          <t>bank_transfer</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'bank_transfer'}</t>
+          <t>bank transfer</t>
         </is>
       </c>
     </row>
@@ -1398,12 +1398,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'credit_card'}</t>
+          <t>credit_card</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'credit_card'}</t>
+          <t>credit card</t>
         </is>
       </c>
     </row>
@@ -1415,12 +1415,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'pending'}</t>
+          <t>pending</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'pending'}</t>
+          <t>pending</t>
         </is>
       </c>
     </row>
@@ -1432,12 +1432,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'confirmed'}</t>
+          <t>confirmed</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'confirmed'}</t>
+          <t>confirmed</t>
         </is>
       </c>
     </row>
@@ -1449,12 +1449,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'cancelled'}</t>
+          <t>cancelled</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'cancelled'}</t>
+          <t>cancelled</t>
         </is>
       </c>
     </row>
@@ -1466,12 +1466,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'chatjimmy'}</t>
+          <t>chatjimmy</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'chatjimmy'}</t>
+          <t>chatjimmy</t>
         </is>
       </c>
     </row>
@@ -1483,12 +1483,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'another_user'}</t>
+          <t>another_user</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'another_user'}</t>
+          <t>another user</t>
         </is>
       </c>
     </row>
